--- a/docs/BOM.xlsx
+++ b/docs/BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dblock/Pictures/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/danielblock/Projects/StoneCold/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B64743DF-DAC2-D843-A4B7-B2817462920F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6727E986-BD86-B147-B0B3-7503DEC89FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13160" yWindow="740" windowWidth="28040" windowHeight="17440" xr2:uid="{2AC8C7AC-316E-754A-97EA-81C14791EFC6}"/>
+    <workbookView xWindow="1360" yWindow="740" windowWidth="28040" windowHeight="17320" xr2:uid="{2AC8C7AC-316E-754A-97EA-81C14791EFC6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="73">
   <si>
     <t>Noctua NH-U12A</t>
   </si>
@@ -243,6 +242,18 @@
   </si>
   <si>
     <t>Extra Stuff I Used</t>
+  </si>
+  <si>
+    <t>Power Barrel Connector Jack 2.50mm ID (0.098"), 5.50mm OD (0.217") Through Hole, Right Angle</t>
+  </si>
+  <si>
+    <t>5.5mm Barrel</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/same-sky-formerly-cui-devices/PJ-082BH/3477156</t>
+  </si>
+  <si>
+    <t>10A is a little under-specced, ideally a non barrel is what should be used</t>
   </si>
 </sst>
 </file>
@@ -252,9 +263,9 @@
   <numFmts count="3">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -303,6 +314,11 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF444444"/>
+      <name val="Roboto"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -325,7 +341,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -334,19 +350,25 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="6" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="8" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -781,7 +803,7 @@
         <v>22.7</v>
       </c>
       <c r="E4" s="8">
-        <f t="shared" ref="E4:E15" si="0">D4*B4</f>
+        <f t="shared" ref="E4:E16" si="0">D4*B4</f>
         <v>22.7</v>
       </c>
       <c r="F4" s="9" t="s">
@@ -1040,10 +1062,34 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" ht="68" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="5">
+        <v>1</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" s="5">
+        <v>1.78</v>
+      </c>
       <c r="E16" s="8">
-        <f>SUM(E2:E15)</f>
-        <v>301.94</v>
+        <f t="shared" si="0"/>
+        <v>1.78</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="E17" s="8">
+        <f>SUM(E2:E16)</f>
+        <v>303.71999999999997</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="25" x14ac:dyDescent="0.25">
@@ -1151,6 +1197,7 @@
     <hyperlink ref="F19" r:id="rId15" xr:uid="{CBD8F8B9-0A55-4D44-A755-AD1ED182EAB1}"/>
     <hyperlink ref="F20" r:id="rId16" xr:uid="{479840FB-FF9F-FC45-8447-C14BC87B88C7}"/>
     <hyperlink ref="F21" r:id="rId17" xr:uid="{59FCA625-FD49-1D4B-9724-C245D3A47E40}"/>
+    <hyperlink ref="F16" r:id="rId18" xr:uid="{461F6EE8-412F-2843-A1B1-EE192008CC29}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
